--- a/data/trans_dic/IP16B98-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero otros medicamentos recetados por el médico</t>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,29; 100,0</t>
+          <t>70,03; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,36; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,73; 100,0</t>
+          <t>79,83; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,6; 100,0</t>
+          <t>76,28; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,4; 100,0</t>
+          <t>84,26; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,64; 100,0</t>
+          <t>90,65; 100,0</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>28,43; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,65; 100,0</t>
+          <t>20,96; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,62; 100,0</t>
+          <t>29,84; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,7; 100,0</t>
+          <t>32,47; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,15; 100,0</t>
+          <t>43,68; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,49; 100,0</t>
+          <t>52,55; 100,0</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,62; 100,0</t>
+          <t>74,38; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,2; 100,0</t>
+          <t>88,45; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,22; 100,0</t>
+          <t>74,58; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,44; 100,0</t>
+          <t>80,27; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,25; 98,26</t>
+          <t>81,86; 97,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,49; 98,77</t>
+          <t>86,74; 98,77</t>
         </is>
       </c>
     </row>
@@ -920,4 +921,587 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3459</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6693</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10149</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14309</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13586</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16387</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23735</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30696</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7547; 10776</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11383; 14259</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13045; 17102</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21093; 25035</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>28476; 31411</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3988</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6194</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7089</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>793; 2788</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>808; 3855</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1518; 5086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1492; 4595</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3439; 7873</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4440; 8450</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21576</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36622</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42690</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12494; 16798</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19164; 21668</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17006; 22803</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18540; 23098</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>32418; 38513</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38830; 44216</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B98-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Estudios-trans_dic.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,03; 100,0</t>
+          <t>74,14; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,83; 100,0</t>
+          <t>71,87; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,28; 100,0</t>
+          <t>80,81; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,26; 100,0</t>
+          <t>83,23; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,65; 100,0</t>
+          <t>86,21; 100,0</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,96; 100,0</t>
+          <t>33,25; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,84; 100,0</t>
+          <t>29,99; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,47; 100,0</t>
+          <t>28,16; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,68; 100,0</t>
+          <t>44,86; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,55; 100,0</t>
+          <t>51,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,38; 100,0</t>
+          <t>77,57; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,45; 100,0</t>
+          <t>86,8; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,27; 100,0</t>
+          <t>80,45; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,86; 97,25</t>
+          <t>82,03; 97,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,74; 98,77</t>
+          <t>86,6; 98,76</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7547; 10776</t>
+          <t>7989; 10776</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1229,22 +1229,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11383; 14259</t>
+          <t>10247; 14259</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13045; 17102</t>
+          <t>13819; 17102</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21093; 25035</t>
+          <t>20836; 25035</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28476; 31411</t>
+          <t>27078; 31411</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>793; 2788</t>
+          <t>0; 2788</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>808; 3855</t>
+          <t>1282; 3855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1518; 5086</t>
+          <t>1525; 5086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1492; 4595</t>
+          <t>1294; 4595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3439; 7873</t>
+          <t>3532; 7873</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4440; 8450</t>
+          <t>4350; 8450</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12494; 16798</t>
+          <t>13030; 16798</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19164; 21668</t>
+          <t>18807; 21668</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17006; 22803</t>
+          <t>17007; 22803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18540; 23098</t>
+          <t>18582; 23098</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32418; 38513</t>
+          <t>32484; 38602</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38830; 44216</t>
+          <t>38766; 44211</t>
         </is>
       </c>
     </row>
